--- a/input/mapping/024. OCB_GOLD_TCKH_V_PR_COLLECTION_PHAT.xlsx
+++ b/input/mapping/024. OCB_GOLD_TCKH_V_PR_COLLECTION_PHAT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/05. DELIVERABLES/00.MAPPING GOLD/OCB_ZONEC_MAPPING_LOGIC_CODE_BATCH_2_20260805/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/01.REVIEWED__OK/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="253" documentId="13_ncr:1_{64928B0C-3199-4446-A4C4-0DE98744620E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{057872DC-75D9-4971-A50A-5C499CA2FC57}"/>
+  <xr:revisionPtr revIDLastSave="255" documentId="13_ncr:1_{64928B0C-3199-4446-A4C4-0DE98744620E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5332EFA6-3FCB-49D0-A2D1-748373926FDE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -52,7 +52,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t>Longnguyen: [14/7]:</t>
         </r>
@@ -61,7 +61,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
 chưa có target catalog và target schema. Bổ sung thêm sau</t>
@@ -161,6 +161,39 @@
 USE SCHEMA tckh;
 CREATE OR REPLACE VIEW v_pr_collection AS
 WITH
+-- ============================================================
+-- SNAPSHOT DUNG CHUNG (tieu chi 2.12): moi bang Silver chi doc DUNG 1 LAN,
+-- gom vao 1 CTE o dau script roi dung lai cho ca 3 nhanh UNION ALL.
+-- Dieu kien loc source_event_date / record_source dat TRONG CTE, khong de
+-- trong ON cua INNER JOIN (tieu chi 2.3).
+-- ============================================================
+-- (A) AR LookupFail=drop — chi kiem tra tai khoan CO TON TAI.
+-- hub_account la DAILY SNAPSHOT: voi &lt;= DATADT thi 1 business_key co NHIEU dong
+-- (1 dong/ngay). Phai DISTINCT truoc khi join, neu khong INNER JOIN se nhan dong
+-- va lam SUM(AMOUNT_LCY) bi thoi phong.
+acct_key AS (
+    SELECT DISTINCT business_key
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_account')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+      AND record_source      = 't24__t24_account'
+),
+-- (B) PST_ENTR_X_AU — semi-join thay cho subquery loc theo dong (tieu chi 2.11).
+-- DISTINCT de giu dung nghia "co phat sinh line movement", khong nhan dong.
+lm_categ AS (
+    SELECT DISTINCT categ_entry_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_line_movement_toanhang_categ_entry')
+    WHERE source_event_date = TO_DATE(:DATADT, 'yyyyMMdd')
+),
+lm_stmt AS (
+    SELECT DISTINCT stmt_entry_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_line_movement_toanhang_stmt_entry')
+    WHERE source_event_date = TO_DATE(:DATADT, 'yyyyMMdd')
+),
+lm_re AS (
+    SELECT DISTINCT re_consol_spec_entry_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_line_movement_toanhang_re_consol_spec_entry')
+    WHERE source_event_date = TO_DATE(:DATADT, 'yyyyMMdd')
+),
 -- ============================================================
 -- CATEG_ENTRY
 -- ============================================================
@@ -220,67 +253,38 @@
 ),
 -- ============================================================
 -- UNION ALL 3 entry types
--- Filter bổ sung (giữ nguyên từ job gốc):
---   (A) INNER JOIN hub_account: replicate AR LookupFail=drop
---   (B) EXISTS link_line_movement_toanhang_*: replicate INNER JOIN PST_ENTR_X_AU
+-- Filter bo sung (giu nguyen y job goc):
+--   (A) JOIN acct_key                    : replicate AR LookupFail=drop
+--   (B) JOIN lm_categ / lm_stmt / lm_re  : replicate INNER JOIN PST_ENTR_X_AU
+-- Ca 2 deu la semi-join tren khoa DISTINCT nen chi LOC, khong nhan dong.
 -- ============================================================
 all_entries AS (
     -- CATEG_ENTRY
     SELECT i.t_our_reference, i.t_amount_lcy, c.t_transaction_code
-    FROM categ_hub                                                  h
-    JOIN categ_info i ON i.categ_entry_hashkey = h.categ_entry_hashkey
-    JOIN categ_cls  c ON c.categ_entry_hashkey = h.categ_entry_hashkey
-    -- (A) AR LookupFail=drop
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_account')          ha
-        ON  ha.business_key       = RIGHT(i.t_our_reference, 12)
-        AND ha.source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
-        AND ha.record_source      = 't24__t24_account'
+    FROM categ_hub h
+    JOIN categ_info i  ON i.categ_entry_hashkey = h.categ_entry_hashkey
+    JOIN categ_cls  c  ON c.categ_entry_hashkey = h.categ_entry_hashkey
+    JOIN lm_categ   lm ON lm.categ_entry_hashkey = h.categ_entry_hashkey
+    JOIN acct_key   ak ON ak.business_key = RIGHT(i.t_our_reference, 12)
     WHERE i.t_our_reference IS NOT NULL
-    -- (B) PST_ENTR_X_AU
-    AND EXISTS (
-        SELECT 1
-        FROM IDENTIFIER(:cleaned || '.raw_vault.link_line_movement_toanhang_categ_entry') lm
-        WHERE lm.categ_entry_hashkey = h.categ_entry_hashkey
-          AND lm.source_event_date   = TO_DATE(:DATADT, 'yyyyMMdd')
-    )
     UNION ALL
     -- STMT_ENTRY
     SELECT i.t_our_reference, i.t_amount_lcy, c.t_transaction_code
-    FROM stmt_hub                                                   h
-    JOIN stmt_info  i ON i.stmt_entry_hashkey = h.stmt_entry_hashkey
-    JOIN stmt_cls   c ON c.stmt_entry_hashkey = h.stmt_entry_hashkey
-    -- (A) AR LookupFail=drop
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_account')          ha
-        ON  ha.business_key       = RIGHT(i.t_our_reference, 12)
-        AND ha.source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
-        AND ha.record_source      = 't24__t24_account'
+    FROM stmt_hub h
+    JOIN stmt_info i  ON i.stmt_entry_hashkey = h.stmt_entry_hashkey
+    JOIN stmt_cls  c  ON c.stmt_entry_hashkey = h.stmt_entry_hashkey
+    JOIN lm_stmt   lm ON lm.stmt_entry_hashkey = h.stmt_entry_hashkey
+    JOIN acct_key  ak ON ak.business_key = RIGHT(i.t_our_reference, 12)
     WHERE i.t_our_reference IS NOT NULL
-    -- (B) PST_ENTR_X_AU
-    AND EXISTS (
-        SELECT 1
-        FROM IDENTIFIER(:cleaned || '.raw_vault.link_line_movement_toanhang_stmt_entry') lm
-        WHERE lm.stmt_entry_hashkey  = h.stmt_entry_hashkey
-          AND lm.source_event_date   = TO_DATE(:DATADT, 'yyyyMMdd')
-    )
     UNION ALL
     -- RE_CONSOL_SPEC_ENTRY
     SELECT i.t_our_reference, i.t_amount_lcy, c.t_transaction_code
-    FROM re_hub                                                     h
-    JOIN re_info    i ON i.re_consol_spec_entry_hashkey = h.re_consol_spec_entry_hashkey
-    JOIN re_cls     c ON c.re_consol_spec_entry_hashkey = h.re_consol_spec_entry_hashkey
-    -- (A) AR LookupFail=drop
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_account')          ha
-        ON  ha.business_key       = RIGHT(i.t_our_reference, 12)
-        AND ha.source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
-        AND ha.record_source      = 't24__t24_account'
+    FROM re_hub h
+    JOIN re_info i  ON i.re_consol_spec_entry_hashkey = h.re_consol_spec_entry_hashkey
+    JOIN re_cls  c  ON c.re_consol_spec_entry_hashkey = h.re_consol_spec_entry_hashkey
+    JOIN lm_re   lm ON lm.re_consol_spec_entry_hashkey = h.re_consol_spec_entry_hashkey
+    JOIN acct_key ak ON ak.business_key = RIGHT(i.t_our_reference, 12)
     WHERE i.t_our_reference IS NOT NULL
-    -- (B) PST_ENTR_X_AU
-    AND EXISTS (
-        SELECT 1
-        FROM IDENTIFIER(:cleaned || '.raw_vault.link_line_movement_toanhang_re_consol_spec_entry') lm
-        WHERE lm.re_consol_spec_entry_hashkey = h.re_consol_spec_entry_hashkey
-          AND lm.source_event_date            = TO_DATE(:DATADT, 'yyyyMMdd')
-    )
 ),
 LOAN_REPAYMENT AS (
     SELECT
@@ -292,7 +296,11 @@
     JOIN TRANS_CODE_TP tc ON e.t_transaction_code = tc.ID
     WHERE tc.TP &lt;&gt; 'ACCR'
 )
-SELECT CDR_DT_ID, LD_NO, ABS(SUM(AMOUNT_LCY)) AS PR_COLLECT_EQ
+-- COALESCE ca 2 phia khi doi soat voi he thong cu (Checklist RVN-OCB #11, tieu chi 2.8)
+SELECT
+    CDR_DT_ID,
+    LD_NO,
+    ABS(SUM(COALESCE(AMOUNT_LCY, 0)))    AS PR_COLLECT_EQ
 FROM LOAN_REPAYMENT
 WHERE PAY_TP = 'PR'
   AND CDR_DT_ID &gt;= 20240701
@@ -600,7 +608,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -612,14 +620,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -676,14 +682,12 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -691,46 +695,41 @@
       <sz val="12"/>
       <color rgb="FF002060"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -943,14 +942,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -960,7 +951,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -991,6 +981,15 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1321,7 +1320,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E27E1F5-3F8D-4B59-92DB-6C96DD7C8DD6}">
   <dimension ref="A1:Q33"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="7.28515625" style="12" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" style="12" customWidth="1"/>
@@ -1335,47 +1334,47 @@
     <col min="22" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:17" ht="30" customHeight="1">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-    </row>
-    <row r="2" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="30" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+    </row>
+    <row r="2" spans="1:17" ht="6" customHeight="1"/>
+    <row r="3" spans="1:17" ht="22.15" customHeight="1">
+      <c r="B3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="G3" s="30" t="s">
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="G3" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="L3" s="31" t="s">
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="L3" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-    </row>
-    <row r="4" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+    </row>
+    <row r="4" spans="1:17" ht="6" customHeight="1">
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -1389,359 +1388,359 @@
       <c r="N4" s="14"/>
       <c r="O4" s="14"/>
     </row>
-    <row r="5" spans="1:17" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="27" t="s">
+    <row r="5" spans="1:17" ht="19.899999999999999" customHeight="1">
+      <c r="B5" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="33" t="s">
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="33" t="s">
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="L5" s="32" t="s">
+      <c r="L5" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32"/>
-    </row>
-    <row r="6" spans="1:17" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="32"/>
-      <c r="O6" s="32"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+    </row>
+    <row r="6" spans="1:17" ht="19.899999999999999" customHeight="1">
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
       <c r="Q6" s="15"/>
     </row>
-    <row r="7" spans="1:17" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32"/>
-    </row>
-    <row r="8" spans="1:17" ht="7.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="32"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="32"/>
-      <c r="O8" s="32"/>
-    </row>
-    <row r="9" spans="1:17" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="32"/>
-    </row>
-    <row r="10" spans="1:17" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="32"/>
-    </row>
-    <row r="11" spans="1:17" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="32"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="32"/>
-      <c r="O11" s="32"/>
-    </row>
-    <row r="12" spans="1:17" ht="7.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="27"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="32"/>
-      <c r="N12" s="32"/>
-      <c r="O12" s="32"/>
-    </row>
-    <row r="13" spans="1:17" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="32"/>
-      <c r="O13" s="32"/>
-    </row>
-    <row r="14" spans="1:17" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
-      <c r="N14" s="32"/>
-      <c r="O14" s="32"/>
-    </row>
-    <row r="15" spans="1:17" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="32"/>
-      <c r="O15" s="32"/>
-    </row>
-    <row r="16" spans="1:17" ht="7.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="32"/>
-      <c r="O16" s="32"/>
-    </row>
-    <row r="17" spans="2:15" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="32"/>
-      <c r="O17" s="32"/>
-    </row>
-    <row r="18" spans="2:15" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="27"/>
-      <c r="J18" s="27"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="32"/>
-      <c r="O18" s="32"/>
-    </row>
-    <row r="19" spans="2:15" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="32"/>
-      <c r="N19" s="32"/>
-      <c r="O19" s="32"/>
-    </row>
-    <row r="20" spans="2:15" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-    </row>
-    <row r="21" spans="2:15" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="27"/>
-      <c r="K21" s="33" t="s">
+    <row r="7" spans="1:17" ht="19.899999999999999" customHeight="1">
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+    </row>
+    <row r="8" spans="1:17" ht="7.15" customHeight="1">
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+    </row>
+    <row r="9" spans="1:17" ht="19.899999999999999" customHeight="1">
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="27"/>
+    </row>
+    <row r="10" spans="1:17" ht="19.899999999999999" customHeight="1">
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
+    </row>
+    <row r="11" spans="1:17" ht="19.899999999999999" customHeight="1">
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
+    </row>
+    <row r="12" spans="1:17" ht="7.15" customHeight="1">
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="27"/>
+    </row>
+    <row r="13" spans="1:17" ht="19.899999999999999" customHeight="1">
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="27"/>
+    </row>
+    <row r="14" spans="1:17" ht="19.899999999999999" customHeight="1">
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="27"/>
+    </row>
+    <row r="15" spans="1:17" ht="19.899999999999999" customHeight="1">
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27"/>
+    </row>
+    <row r="16" spans="1:17" ht="7.15" customHeight="1">
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
+    </row>
+    <row r="17" spans="2:15" ht="19.899999999999999" customHeight="1">
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="27"/>
+    </row>
+    <row r="18" spans="2:15" ht="19.899999999999999" customHeight="1">
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="27"/>
+      <c r="O18" s="27"/>
+    </row>
+    <row r="19" spans="2:15" ht="19.899999999999999" customHeight="1">
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="27"/>
+    </row>
+    <row r="20" spans="2:15" ht="10.15" customHeight="1">
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
+    </row>
+    <row r="21" spans="2:15" ht="19.899999999999999" customHeight="1">
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="L21" s="26" t="s">
+      <c r="L21" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="26"/>
-      <c r="N21" s="26"/>
-      <c r="O21" s="26"/>
-    </row>
-    <row r="22" spans="2:15" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="26"/>
-      <c r="M22" s="26"/>
-      <c r="N22" s="26"/>
-      <c r="O22" s="26"/>
-    </row>
-    <row r="23" spans="2:15" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
-    </row>
-    <row r="24" spans="2:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+    </row>
+    <row r="22" spans="2:15" ht="19.899999999999999" customHeight="1">
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+    </row>
+    <row r="23" spans="2:15" ht="19.899999999999999" customHeight="1">
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+    </row>
+    <row r="24" spans="2:15" ht="15.6" customHeight="1"/>
+    <row r="25" spans="2:15" ht="19.5" customHeight="1">
       <c r="G25" s="16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:15" ht="19.5" customHeight="1">
       <c r="G26" s="17"/>
-      <c r="H26" s="22" t="s">
+      <c r="H26" s="36" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:15" ht="19.5" customHeight="1">
       <c r="G27" s="18"/>
-      <c r="H27" s="22" t="s">
+      <c r="H27" s="36" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:15" ht="19.5" customHeight="1">
       <c r="G28" s="19"/>
-      <c r="H28" s="22" t="s">
+      <c r="H28" s="36" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:15" ht="19.5" customHeight="1">
       <c r="G29" s="20"/>
-      <c r="H29" s="22" t="s">
+      <c r="H29" s="36" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:15" ht="19.5" customHeight="1">
       <c r="G30" s="21"/>
-      <c r="H30" s="22" t="s">
+      <c r="H30" s="36" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" s="12" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="2:15" ht="18" customHeight="1"/>
+    <row r="32" spans="2:15" ht="18" customHeight="1"/>
+    <row r="33" s="12" customFormat="1" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="L21:O23"/>
@@ -1763,7 +1762,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FB686A3-9D8C-401B-BB17-D5A81DC82A28}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
@@ -1771,7 +1770,7 @@
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="14.45" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>15</v>
       </c>
@@ -1782,7 +1781,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="22.5" customHeight="1">
       <c r="A2" s="9" t="s">
         <v>18</v>
       </c>
@@ -1793,7 +1792,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="9" t="s">
         <v>20</v>
       </c>
@@ -1804,10 +1803,10 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="23"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="23"/>
+    <row r="4" spans="1:3">
+      <c r="A4" s="37"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="37"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1818,7 +1817,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="64.5703125" style="1" customWidth="1"/>
@@ -1828,16 +1827,16 @@
     <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:5" ht="35.25" customHeight="1">
+      <c r="A1" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-    </row>
-    <row r="2" spans="1:5" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+    </row>
+    <row r="2" spans="1:5" ht="19.899999999999999" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>23</v>
       </c>
@@ -1854,7 +1853,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="86.25" customHeight="1">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -1869,7 +1868,7 @@
       </c>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" spans="1:5" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="77.25" customHeight="1">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -1884,7 +1883,7 @@
       </c>
       <c r="E4" s="6"/>
     </row>
-    <row r="5" spans="1:5" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="72.75" customHeight="1">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -1899,7 +1898,7 @@
       </c>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="85.5" customHeight="1">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -1914,7 +1913,7 @@
       </c>
       <c r="E6" s="6"/>
     </row>
-    <row r="7" spans="1:5" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="80.25" customHeight="1">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -1929,7 +1928,7 @@
       </c>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:5" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="80.25" customHeight="1">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -1944,7 +1943,7 @@
       </c>
       <c r="E8" s="6"/>
     </row>
-    <row r="9" spans="1:5" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="91.5" customHeight="1">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -1959,7 +1958,7 @@
       </c>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" spans="1:5" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="90.75" customHeight="1">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -1974,7 +1973,7 @@
       </c>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" spans="1:5" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="91.5" customHeight="1">
       <c r="A11" s="4">
         <v>9</v>
       </c>
@@ -1989,7 +1988,7 @@
       </c>
       <c r="E11" s="6"/>
     </row>
-    <row r="12" spans="1:5" ht="373.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="373.5" customHeight="1">
       <c r="A12" s="4">
         <v>10</v>
       </c>
@@ -2004,7 +2003,7 @@
       </c>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" spans="1:5" ht="267" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="267" customHeight="1">
       <c r="A13" s="4">
         <v>11</v>
       </c>
@@ -2021,7 +2020,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="31.15" customHeight="1">
       <c r="A14" s="4">
         <v>12</v>
       </c>
@@ -2038,23 +2037,23 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-    </row>
-    <row r="16" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="36" t="s">
+    <row r="15" spans="1:5" ht="6" customHeight="1">
+      <c r="A15" s="39"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+    </row>
+    <row r="16" spans="1:5" ht="13.9" customHeight="1">
+      <c r="A16" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-    </row>
-    <row r="17" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+    </row>
+    <row r="17" spans="1:5" ht="26.45" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>57</v>
       </c>
@@ -2071,7 +2070,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="24.75" customHeight="1">
       <c r="A18" s="5" t="s">
         <v>62</v>
       </c>
@@ -2088,7 +2087,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="24.75" customHeight="1">
       <c r="A19" s="5" t="s">
         <v>62</v>
       </c>
@@ -2105,7 +2104,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="24.75" customHeight="1">
       <c r="A20" s="5" t="s">
         <v>62</v>
       </c>
@@ -2122,12 +2121,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="24"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
+    <row r="21" spans="1:5">
+      <c r="A21" s="38"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2141,7 +2140,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A44D65C7-006F-4346-A1AB-A2DBFD7E6D3B}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="38" style="1" customWidth="1"/>
@@ -2149,19 +2148,19 @@
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25"/>
-      <c r="B1" s="25"/>
-      <c r="C1" s="24"/>
-    </row>
-    <row r="2" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
+    <row r="1" spans="1:3" ht="6" customHeight="1">
+      <c r="A1" s="39"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="38"/>
+    </row>
+    <row r="2" spans="1:3" ht="13.9" customHeight="1">
+      <c r="A2" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-    </row>
-    <row r="3" spans="1:3" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+    </row>
+    <row r="3" spans="1:3" ht="26.45" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>16</v>
       </c>
@@ -2172,7 +2171,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="15.75" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -2183,7 +2182,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -2194,7 +2193,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -2205,7 +2204,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -2225,6 +2224,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -2396,7 +2405,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2405,48 +2414,14 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAB87AE6-A245-4FB4-BBAA-0FB557CB0D1A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F3D2864-F6F9-4B8C-BD0D-BF1620E53370}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04880426-9B18-41D0-A581-7E9ED8919F39}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAB87AE6-A245-4FB4-BBAA-0FB557CB0D1A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F3D2864-F6F9-4B8C-BD0D-BF1620E53370}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04880426-9B18-41D0-A581-7E9ED8919F39}"/>
 </file>
--- a/input/mapping/024. OCB_GOLD_TCKH_V_PR_COLLECTION_PHAT.xlsx
+++ b/input/mapping/024. OCB_GOLD_TCKH_V_PR_COLLECTION_PHAT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/01.REVIEWED__OK/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="255" documentId="13_ncr:1_{64928B0C-3199-4446-A4C4-0DE98744620E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5332EFA6-3FCB-49D0-A2D1-748373926FDE}"/>
+  <xr:revisionPtr revIDLastSave="257" documentId="13_ncr:1_{64928B0C-3199-4446-A4C4-0DE98744620E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B783A3B6-C6B3-41BF-B148-2ED9D1F0002A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -157,28 +157,16 @@
     <t>Code mới</t>
   </si>
   <si>
-    <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
+    <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
 CREATE OR REPLACE VIEW v_pr_collection AS
 WITH
--- ============================================================
--- SNAPSHOT DUNG CHUNG (tieu chi 2.12): moi bang Silver chi doc DUNG 1 LAN,
--- gom vao 1 CTE o dau script roi dung lai cho ca 3 nhanh UNION ALL.
--- Dieu kien loc source_event_date / record_source dat TRONG CTE, khong de
--- trong ON cua INNER JOIN (tieu chi 2.3).
--- ============================================================
--- (A) AR LookupFail=drop — chi kiem tra tai khoan CO TON TAI.
--- hub_account la DAILY SNAPSHOT: voi &lt;= DATADT thi 1 business_key co NHIEU dong
--- (1 dong/ngay). Phai DISTINCT truoc khi join, neu khong INNER JOIN se nhan dong
--- va lam SUM(AMOUNT_LCY) bi thoi phong.
 acct_key AS (
     SELECT DISTINCT business_key
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_account')
     WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
       AND record_source      = 't24__t24_account'
 ),
--- (B) PST_ENTR_X_AU — semi-join thay cho subquery loc theo dong (tieu chi 2.11).
--- DISTINCT de giu dung nghia "co phat sinh line movement", khong nhan dong.
 lm_categ AS (
     SELECT DISTINCT categ_entry_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.link_line_movement_toanhang_categ_entry')
@@ -194,9 +182,6 @@
     FROM IDENTIFIER(:cleaned || '.raw_vault.link_line_movement_toanhang_re_consol_spec_entry')
     WHERE source_event_date = TO_DATE(:DATADT, 'yyyyMMdd')
 ),
--- ============================================================
--- CATEG_ENTRY
--- ============================================================
 categ_hub AS (
     SELECT categ_entry_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_categ_entry')
@@ -213,9 +198,6 @@
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_categ_entry_classification')
     WHERE source_event_date = TO_DATE(:DATADT, 'yyyyMMdd')
 ),
--- ============================================================
--- STMT_ENTRY
--- ============================================================
 stmt_hub AS (
     SELECT stmt_entry_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_stmt_entry')
@@ -232,9 +214,6 @@
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_stmt_entry_classification')
     WHERE source_event_date = TO_DATE(:DATADT, 'yyyyMMdd')
 ),
--- ============================================================
--- RE_CONSOL_SPEC_ENTRY
--- ============================================================
 re_hub AS (
     SELECT re_consol_spec_entry_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_re_consol_spec_entry')
@@ -251,15 +230,7 @@
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_re_consol_spec_entry_classification')
     WHERE source_event_date = TO_DATE(:DATADT, 'yyyyMMdd')
 ),
--- ============================================================
--- UNION ALL 3 entry types
--- Filter bo sung (giu nguyen y job goc):
---   (A) JOIN acct_key                    : replicate AR LookupFail=drop
---   (B) JOIN lm_categ / lm_stmt / lm_re  : replicate INNER JOIN PST_ENTR_X_AU
--- Ca 2 deu la semi-join tren khoa DISTINCT nen chi LOC, khong nhan dong.
--- ============================================================
 all_entries AS (
-    -- CATEG_ENTRY
     SELECT i.t_our_reference, i.t_amount_lcy, c.t_transaction_code
     FROM categ_hub h
     JOIN categ_info i  ON i.categ_entry_hashkey = h.categ_entry_hashkey
@@ -268,7 +239,6 @@
     JOIN acct_key   ak ON ak.business_key = RIGHT(i.t_our_reference, 12)
     WHERE i.t_our_reference IS NOT NULL
     UNION ALL
-    -- STMT_ENTRY
     SELECT i.t_our_reference, i.t_amount_lcy, c.t_transaction_code
     FROM stmt_hub h
     JOIN stmt_info i  ON i.stmt_entry_hashkey = h.stmt_entry_hashkey
@@ -277,7 +247,6 @@
     JOIN acct_key  ak ON ak.business_key = RIGHT(i.t_our_reference, 12)
     WHERE i.t_our_reference IS NOT NULL
     UNION ALL
-    -- RE_CONSOL_SPEC_ENTRY
     SELECT i.t_our_reference, i.t_amount_lcy, c.t_transaction_code
     FROM re_hub h
     JOIN re_info i  ON i.re_consol_spec_entry_hashkey = h.re_consol_spec_entry_hashkey
@@ -296,7 +265,6 @@
     JOIN TRANS_CODE_TP tc ON e.t_transaction_code = tc.ID
     WHERE tc.TP &lt;&gt; 'ACCR'
 )
--- COALESCE ca 2 phia khi doi soat voi he thong cu (Checklist RVN-OCB #11, tieu chi 2.8)
 SELECT
     CDR_DT_ID,
     LD_NO,
@@ -304,8 +272,7 @@
 FROM LOAN_REPAYMENT
 WHERE PAY_TP = 'PR'
   AND CDR_DT_ID &gt;= 20240701
-GROUP BY CDR_DT_ID, LD_NO;
-</t>
+GROUP BY CDR_DT_ID, LD_NO;</t>
   </si>
   <si>
     <t>V_PR_COLLECTION
@@ -2224,13 +2191,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2406,16 +2372,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F3D2864-F6F9-4B8C-BD0D-BF1620E53370}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04880426-9B18-41D0-A581-7E9ED8919F39}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2423,5 +2390,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04880426-9B18-41D0-A581-7E9ED8919F39}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F3D2864-F6F9-4B8C-BD0D-BF1620E53370}"/>
 </file>